--- a/opendata.xlsx
+++ b/opendata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19271" windowHeight="10187"/>
+    <workbookView windowWidth="24180" windowHeight="12915"/>
   </bookViews>
   <sheets>
     <sheet name="list" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65">
   <si>
     <t>名稱</t>
   </si>
@@ -206,6 +206,15 @@
     <t>https://data.fda.gov.tw/data/opendata/export/4/csv</t>
   </si>
   <si>
+    <t>醫療服務給付項目及支付標準</t>
+  </si>
+  <si>
+    <t>https://data.gov.tw/dataset/174450</t>
+  </si>
+  <si>
+    <t>https://info.nhi.gov.tw/api/iode0000s01/Dataset?rId=A21030000I-D20021-001</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -345,10 +354,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -379,35 +388,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="新細明體"/>
@@ -415,8 +395,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="新細明體"/>
       <charset val="134"/>
@@ -431,6 +418,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -440,24 +434,24 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="新細明體"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -466,14 +460,6 @@
       <color theme="1"/>
       <name val="新細明體"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="新細明體"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -494,14 +480,44 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -517,14 +533,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -539,7 +548,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,25 +590,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,91 +710,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,43 +728,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,21 +739,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -807,6 +801,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -822,159 +825,165 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1309,13 +1318,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E1003"/>
-  <sheetFormatPr defaultColWidth="12.5740740740741" defaultRowHeight="23.1" customHeight="1" outlineLevelCol="4"/>
+  <dimension ref="A1:E1004"/>
+  <sheetFormatPr defaultColWidth="12.5714285714286" defaultRowHeight="23.1" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="42.5740740740741" style="1" customWidth="1"/>
-    <col min="2" max="2" width="44.1388888888889" customWidth="1"/>
-    <col min="3" max="3" width="46.8611111111111" customWidth="1"/>
-    <col min="6" max="25" width="12.5740740740741" style="2"/>
+    <col min="1" max="1" width="42.5714285714286" style="1" customWidth="1"/>
+    <col min="2" max="2" width="44.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="46.8571428571429" customWidth="1"/>
+    <col min="6" max="25" width="12.5714285714286" style="2"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:5">
@@ -1550,9 +1559,11 @@
       <c r="B16" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="D16" s="7" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E16" s="5"/>
     </row>
@@ -1561,24 +1572,24 @@
         <v>51</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E17" s="5"/>
     </row>
     <row r="18" customHeight="1" spans="1:5">
       <c r="A18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -1586,26 +1597,24 @@
       <c r="A19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>56</v>
       </c>
       <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
+      <c r="D19" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="E19" s="5"/>
     </row>
     <row r="20" customHeight="1" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>7</v>
-      </c>
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="5"/>
     </row>
     <row r="21" customHeight="1" spans="1:5">
@@ -1613,25 +1622,34 @@
         <v>60</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" customHeight="1" spans="2:5">
-      <c r="B22" s="2"/>
-      <c r="D22" s="7"/>
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23" customHeight="1" spans="2:5">
       <c r="B23" s="2"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="2"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="2"/>
     </row>
     <row r="24" customHeight="1" spans="2:5">
@@ -1648,7 +1666,7 @@
     </row>
     <row r="26" customHeight="1" spans="2:5">
       <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
+      <c r="C26" s="6"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
     </row>
@@ -7513,6 +7531,12 @@
       <c r="C1003" s="2"/>
       <c r="D1003" s="2"/>
       <c r="E1003" s="2"/>
+    </row>
+    <row r="1004" customHeight="1" spans="2:5">
+      <c r="B1004" s="2"/>
+      <c r="C1004" s="2"/>
+      <c r="D1004" s="2"/>
+      <c r="E1004" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7538,19 +7562,21 @@
     <hyperlink ref="C12" r:id="rId20" display="https://data.fda.gov.tw/opendata/exportDataList.do?method=ExportData&amp;InfoId=19&amp;logType=2"/>
     <hyperlink ref="B9" r:id="rId21" display="https://data.gov.tw/dataset/9576"/>
     <hyperlink ref="C9" r:id="rId22" display="https://data.fda.gov.tw/opendata/exportDataList.do?method=ExportData&amp;InfoId=68&amp;logType=2"/>
-    <hyperlink ref="B16" r:id="rId23" display="https://www.nhi.gov.tw/ch/cp-14300-03585-2467-1.html"/>
     <hyperlink ref="B17" r:id="rId23" display="https://www.nhi.gov.tw/ch/cp-14300-03585-2467-1.html"/>
+    <hyperlink ref="B18" r:id="rId23" display="https://www.nhi.gov.tw/ch/cp-14300-03585-2467-1.html"/>
     <hyperlink ref="B5" r:id="rId24" display="https://data.gov.tw/dataset/9120"/>
     <hyperlink ref="C5" r:id="rId25" display="https://data.fda.gov.tw/opendata/exportDataList.do?method=ExportData&amp;InfoId=42&amp;logType=2"/>
     <hyperlink ref="B15" r:id="rId26" display="https://data.gov.tw/dataset/8452"/>
     <hyperlink ref="C15" r:id="rId27" display="https://data.fda.gov.tw/data/opendata/export/4/csv"/>
-    <hyperlink ref="B20" r:id="rId28" display="https://terms.naer.edu.tw/download/1/"/>
     <hyperlink ref="B21" r:id="rId28" display="https://terms.naer.edu.tw/download/1/"/>
-    <hyperlink ref="C21" r:id="rId29" display="https://terms.naer.edu.tw/media/terms_data/1/%E8%97%A5%E5%AD%B8-%E8%97%A5%E7%89%A9%E5%90%8D%E7%A8%B1%E5%A3%93%E7%B8%AE%E6%AA%94.zip"/>
-    <hyperlink ref="C20" r:id="rId30" display="https://terms.naer.edu.tw/media/terms_data/1/%E8%97%A5%E5%AD%B8%E5%A3%93%E7%B8%AE%E6%AA%94_TgjVhQY.zip"/>
+    <hyperlink ref="B22" r:id="rId28" display="https://terms.naer.edu.tw/download/1/"/>
+    <hyperlink ref="C22" r:id="rId29" display="https://terms.naer.edu.tw/media/terms_data/1/%E8%97%A5%E5%AD%B8-%E8%97%A5%E7%89%A9%E5%90%8D%E7%A8%B1%E5%A3%93%E7%B8%AE%E6%AA%94.zip"/>
+    <hyperlink ref="C21" r:id="rId30" display="https://terms.naer.edu.tw/media/terms_data/1/%E8%97%A5%E5%AD%B8%E5%A3%93%E7%B8%AE%E6%AA%94_TgjVhQY.zip"/>
     <hyperlink ref="B10" r:id="rId31" display="https://data.gov.tw/dataset/9578"/>
     <hyperlink ref="C10" r:id="rId32" display="https://data.fda.gov.tw/data/opendata/export/70/csv"/>
-    <hyperlink ref="B18" r:id="rId33" display="https://service.mohw.gov.tw/DOCMAP/CusSite/TCMLQueryForm.aspx"/>
+    <hyperlink ref="B19" r:id="rId33" display="https://service.mohw.gov.tw/DOCMAP/CusSite/TCMLQueryForm.aspx"/>
+    <hyperlink ref="B16" r:id="rId34" display="https://data.gov.tw/dataset/174450" tooltip="https://data.gov.tw/dataset/174450"/>
+    <hyperlink ref="C16" r:id="rId35" display="https://info.nhi.gov.tw/api/iode0000s01/Dataset?rId=A21030000I-D20021-001" tooltip="https://info.nhi.gov.tw/api/iode0000s01/Dataset?rId=A21030000I-D20021-001"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <headerFooter/>

--- a/opendata.xlsx
+++ b/opendata.xlsx
@@ -317,7 +317,7 @@
     <t>https://terms.naer.edu.tw/download/1/</t>
   </si>
   <si>
-    <t>https://terms.naer.edu.tw/media/terms_data/1/%E8%97%A5%E5%AD%B8%E5%A3%93%E7%B8%AE%E6%AA%94_TgjVhQY.zip</t>
+    <t>https://terms.naer.edu.tw/media/terms_data/1/%E8%97%A5%E5%AD%B8%E5%A3%93%E7%B8%AE%E6%AA%94_KaFonff.zip</t>
   </si>
   <si>
     <r>
@@ -354,9 +354,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="25">
@@ -388,36 +388,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="新細明體"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="新細明體"/>
@@ -433,6 +403,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="新細明體"/>
@@ -440,8 +425,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -456,14 +456,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="新細明體"/>
@@ -471,53 +463,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="新細明體"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -538,6 +494,50 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -548,13 +548,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,31 +608,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,49 +626,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -662,49 +650,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -716,19 +728,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,30 +743,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -777,35 +753,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -825,6 +772,39 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -839,151 +819,171 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -7571,7 +7571,7 @@
     <hyperlink ref="B21" r:id="rId28" display="https://terms.naer.edu.tw/download/1/"/>
     <hyperlink ref="B22" r:id="rId28" display="https://terms.naer.edu.tw/download/1/"/>
     <hyperlink ref="C22" r:id="rId29" display="https://terms.naer.edu.tw/media/terms_data/1/%E8%97%A5%E5%AD%B8-%E8%97%A5%E7%89%A9%E5%90%8D%E7%A8%B1%E5%A3%93%E7%B8%AE%E6%AA%94.zip"/>
-    <hyperlink ref="C21" r:id="rId30" display="https://terms.naer.edu.tw/media/terms_data/1/%E8%97%A5%E5%AD%B8%E5%A3%93%E7%B8%AE%E6%AA%94_TgjVhQY.zip"/>
+    <hyperlink ref="C21" r:id="rId30" display="https://terms.naer.edu.tw/media/terms_data/1/%E8%97%A5%E5%AD%B8%E5%A3%93%E7%B8%AE%E6%AA%94_KaFonff.zip" tooltip="https://terms.naer.edu.tw/media/terms_data/1/%E8%97%A5%E5%AD%B8%E5%A3%93%E7%B8%AE%E6%AA%94_KaFonff.zip"/>
     <hyperlink ref="B10" r:id="rId31" display="https://data.gov.tw/dataset/9578"/>
     <hyperlink ref="C10" r:id="rId32" display="https://data.fda.gov.tw/data/opendata/export/70/csv"/>
     <hyperlink ref="B19" r:id="rId33" display="https://service.mohw.gov.tw/DOCMAP/CusSite/TCMLQueryForm.aspx"/>

--- a/opendata.xlsx
+++ b/opendata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24180" windowHeight="12915"/>
+    <workbookView windowWidth="28080" windowHeight="12915"/>
   </bookViews>
   <sheets>
     <sheet name="list" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75">
   <si>
     <t>名稱</t>
   </si>
@@ -282,10 +282,13 @@
     <t>xls</t>
   </si>
   <si>
-    <t>自有藥品明細</t>
+    <t>自有藥品明細表</t>
   </si>
   <si>
-    <t>自備</t>
+    <t>欄位範例</t>
+  </si>
+  <si>
+    <t>https://github.com/nedewei/TBfiles/raw/main/%E8%87%AA%E6%9C%89%E8%97%A5%E5%93%81%E6%98%8E%E7%B4%B0%E8%A1%A8.xlsx</t>
   </si>
   <si>
     <r>
@@ -348,15 +351,42 @@
   <si>
     <t>https://terms.naer.edu.tw/media/terms_data/1/%E8%97%A5%E5%AD%B8-%E8%97%A5%E7%89%A9%E5%90%8D%E7%A8%B1%E5%A3%93%E7%B8%AE%E6%AA%94.zip</t>
   </si>
+  <si>
+    <t>藥品短缺-有替代</t>
+  </si>
+  <si>
+    <t>https://data.gov.tw/dataset/54504</t>
+  </si>
+  <si>
+    <t>https://data.fda.gov.tw/data/opendata/export/104/csv</t>
+  </si>
+  <si>
+    <t>藥品短缺-無替代</t>
+  </si>
+  <si>
+    <t>https://data.gov.tw/dataset/54505</t>
+  </si>
+  <si>
+    <t>https://data.fda.gov.tw/data/opendata/export/105/csv</t>
+  </si>
+  <si>
+    <t>藥品短缺-已解除</t>
+  </si>
+  <si>
+    <t>https://data.gov.tw/dataset/54506</t>
+  </si>
+  <si>
+    <t>https://data.fda.gov.tw/data/opendata/export/106/csv</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="25">
@@ -388,13 +418,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -403,23 +426,74 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -433,6 +507,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="新細明體"/>
@@ -440,15 +515,8 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="新細明體"/>
       <charset val="134"/>
@@ -463,54 +531,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="新細明體"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="新細明體"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="新細明體"/>
@@ -525,15 +554,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="新細明體"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -548,7 +578,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,7 +596,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,7 +632,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,13 +650,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,7 +662,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,7 +698,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,49 +734,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -684,54 +762,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -739,6 +769,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -753,6 +807,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -774,8 +837,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -804,190 +869,155 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1002,6 +1032,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1613,19 +1644,21 @@
       <c r="B20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="D20" s="7"/>
       <c r="E20" s="5"/>
     </row>
     <row r="21" customHeight="1" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>7</v>
@@ -1634,34 +1667,62 @@
     </row>
     <row r="22" customHeight="1" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" customHeight="1" spans="2:5">
-      <c r="B23" s="2"/>
-      <c r="D23" s="7"/>
+    <row r="23" customHeight="1" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" customHeight="1" spans="2:5">
-      <c r="B24" s="2"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="2"/>
+    <row r="24" customHeight="1" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" customHeight="1" spans="2:5">
-      <c r="B25" s="2"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="2"/>
+    <row r="25" customHeight="1" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26" customHeight="1" spans="2:5">
@@ -7577,6 +7638,7 @@
     <hyperlink ref="B19" r:id="rId33" display="https://service.mohw.gov.tw/DOCMAP/CusSite/TCMLQueryForm.aspx"/>
     <hyperlink ref="B16" r:id="rId34" display="https://data.gov.tw/dataset/174450" tooltip="https://data.gov.tw/dataset/174450"/>
     <hyperlink ref="C16" r:id="rId35" display="https://info.nhi.gov.tw/api/iode0000s01/Dataset?rId=A21030000I-D20021-001" tooltip="https://info.nhi.gov.tw/api/iode0000s01/Dataset?rId=A21030000I-D20021-001"/>
+    <hyperlink ref="C20" r:id="rId36" display="https://github.com/nedewei/TBfiles/raw/main/%E8%87%AA%E6%9C%89%E8%97%A5%E5%93%81%E6%98%8E%E7%B4%B0%E8%A1%A8.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <headerFooter/>
